--- a/data/trans_orig/P25F_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P25F_2023-Provincia-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el modo de empleo para el que utilizan los cigarrillos electrónicos en 2023</t>
+          <t>Población según el modo de empleo para el que utilizan los cigarrillos electrónicos en 2023 (tasa de respuesta: 90,41%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -735,7 +735,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8118</t>
+          <t>8597</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>64,05%</t>
+          <t>67,83%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>540</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -805,7 +805,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7955</t>
+          <t>6711</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>58,39%</t>
+          <t>49,26%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>344</t>
+          <t>347</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12522</t>
+          <t>12431</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>540</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>375</t>
+          <t>633</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>12676</t>
+          <t>13089</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,05%</t>
+          <t>96,08%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>117</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9138</t>
+          <t>9983</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>72,1%</t>
+          <t>78,77%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>540</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1031,7 +1031,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>9066</t>
+          <t>9090</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>66,55%</t>
+          <t>66,73%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2946</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>540</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2552</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2946</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,39 +1217,39 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>409</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
           <t>949</t>
         </is>
       </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>43,07%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>949</t>
-        </is>
-      </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -1257,7 +1257,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4229</t>
+          <t>3780</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>31,04%</t>
+          <t>27,75%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4088</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1452,7 +1452,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3670</t>
+          <t>2951</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>73,94%</t>
+          <t>59,46%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1487,7 +1487,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6089</t>
+          <t>3883</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>11,71%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8473</t>
+          <t>7902</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>26744</t>
+          <t>25712</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>30,06%</t>
+          <t>28,04%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,9%</t>
+          <t>91,23%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1311</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>8575</t>
+          <t>8116</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>27454</t>
+          <t>27937</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>25,87%</t>
+          <t>24,49%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>82,83%</t>
+          <t>84,29%</t>
         </is>
       </c>
     </row>
@@ -1643,7 +1643,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>15098</t>
+          <t>13964</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>53,57%</t>
+          <t>49,55%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1311</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1713,7 +1713,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>13162</t>
+          <t>16444</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>39,71%</t>
+          <t>49,61%</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16475</t>
+          <t>16097</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1771,7 +1771,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>58,46%</t>
+          <t>57,12%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1311</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>16237</t>
+          <t>16115</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1841,7 +1841,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>48,99%</t>
+          <t>48,62%</t>
         </is>
       </c>
     </row>
@@ -1869,7 +1869,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>8192</t>
+          <t>8338</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1884,7 +1884,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>29,07%</t>
+          <t>29,59%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,7 +1899,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1293</t>
+          <t>2130</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>26,06%</t>
+          <t>42,91%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1961</t>
+          <t>1762</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>14678</t>
+          <t>14008</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>44,28%</t>
+          <t>42,26%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1987</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>882</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1642</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1987</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>882</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1642</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1987</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2335,12 +2335,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2360,7 +2360,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>2272</t>
+          <t>1896</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2375,7 +2375,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>93,4%</t>
+          <t>77,92%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2395,7 +2395,7 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>3784</t>
+          <t>3441</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>47,81%</t>
+          <t>43,48%</t>
         </is>
       </c>
     </row>
@@ -2468,12 +2468,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>882</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2508,7 +2508,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5261</t>
+          <t>5912</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>66,47%</t>
+          <t>74,69%</t>
         </is>
       </c>
     </row>
@@ -2581,7 +2581,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>537</t>
+          <t>351</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>22,08%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1990</t>
+          <t>1970</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>7393</t>
+          <t>7331</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>25,14%</t>
+          <t>24,89%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>93,4%</t>
+          <t>92,62%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2314</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>44,41%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1624</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2045</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2924,12 +2924,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>644</t>
+          <t>671</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>7136</t>
+          <t>7163</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>91,16%</t>
+          <t>91,51%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2959,12 +2959,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2115</t>
+          <t>1868</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>11414</t>
+          <t>11248</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>87,55%</t>
+          <t>86,28%</t>
         </is>
       </c>
     </row>
@@ -3002,12 +3002,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2314</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3017,12 +3017,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>44,41%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3042,7 +3042,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>6081</t>
+          <t>5684</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3057,7 +3057,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>77,68%</t>
+          <t>72,61%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3077,7 +3077,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>7364</t>
+          <t>6952</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3092,7 +3092,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>56,49%</t>
+          <t>53,33%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2314</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>44,41%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3155,7 +3155,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>3650</t>
+          <t>4175</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3170,7 +3170,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>46,63%</t>
+          <t>53,33%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3190,7 +3190,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4411</t>
+          <t>4391</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3205,7 +3205,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>33,84%</t>
+          <t>33,68%</t>
         </is>
       </c>
     </row>
@@ -3233,7 +3233,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>5210</t>
+          <t>5043</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3248,7 +3248,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3268,7 +3268,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>5582</t>
+          <t>6221</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>71,3%</t>
+          <t>79,47%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>170</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>9755</t>
+          <t>9331</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>74,83%</t>
+          <t>71,57%</t>
         </is>
       </c>
     </row>
@@ -3458,12 +3458,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>780</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3473,12 +3473,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3498,7 +3498,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1854</t>
+          <t>1863</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3513,7 +3513,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>59,96%</t>
+          <t>60,25%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3533,7 +3533,7 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2244</t>
+          <t>1944</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3548,7 +3548,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>50,28%</t>
+          <t>43,56%</t>
         </is>
       </c>
     </row>
@@ -3606,12 +3606,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>398</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2700</t>
+          <t>2697</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3621,12 +3621,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>87,28%</t>
+          <t>87,18%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3641,12 +3641,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>674</t>
+          <t>633</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>3611</t>
+          <t>3614</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3656,12 +3656,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>80,91%</t>
+          <t>80,97%</t>
         </is>
       </c>
     </row>
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>780</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3699,12 +3699,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1431</t>
+          <t>1836</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3739,7 +3739,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>46,27%</t>
+          <t>59,35%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3759,7 +3759,7 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1912</t>
+          <t>2277</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3774,7 +3774,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>42,84%</t>
+          <t>51,02%</t>
         </is>
       </c>
     </row>
@@ -3797,12 +3797,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>780</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3812,12 +3812,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3832,12 +3832,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>719</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3847,12 +3847,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3867,12 +3867,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>836</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3882,12 +3882,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3950,7 +3950,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>1813</t>
+          <t>2003</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>58,6%</t>
+          <t>64,77%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3980,12 +3980,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>380</t>
+          <t>377</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>3245</t>
+          <t>3181</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>72,71%</t>
+          <t>71,28%</t>
         </is>
       </c>
     </row>
@@ -4140,12 +4140,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4155,12 +4155,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4175,12 +4175,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>1187</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4190,12 +4190,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>44,41%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4210,12 +4210,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>1275</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4225,12 +4225,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4253,12 +4253,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4268,12 +4268,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4328,7 +4328,7 @@
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>2998</t>
+          <t>3075</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4343,7 +4343,7 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>85,22%</t>
+          <t>87,4%</t>
         </is>
       </c>
     </row>
@@ -4366,12 +4366,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4381,12 +4381,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4401,12 +4401,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>1187</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4416,12 +4416,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>44,41%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4436,12 +4436,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>1275</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4451,12 +4451,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4479,12 +4479,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4494,12 +4494,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4514,12 +4514,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>1187</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4529,12 +4529,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>44,41%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4549,12 +4549,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>1275</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4564,12 +4564,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4592,12 +4592,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>193</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>845</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4607,12 +4607,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4662,7 +4662,7 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>207</t>
+          <t>520</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
@@ -4677,7 +4677,7 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
@@ -4827,7 +4827,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>8062</t>
+          <t>8549</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4842,7 +4842,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>29,72%</t>
+          <t>31,52%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4862,7 +4862,7 @@
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>11350</t>
+          <t>11231</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4877,7 +4877,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>62,89%</t>
+          <t>62,23%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4892,12 +4892,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>1646</t>
+          <t>1338</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>15196</t>
+          <t>14664</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4907,12 +4907,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>33,64%</t>
+          <t>32,46%</t>
         </is>
       </c>
     </row>
@@ -4935,12 +4935,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>6508</t>
+          <t>7265</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>21435</t>
+          <t>22237</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4950,12 +4950,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>23,99%</t>
+          <t>26,78%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>79,02%</t>
+          <t>81,98%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4970,12 +4970,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>470</t>
+          <t>383</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>11373</t>
+          <t>11119</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>63,02%</t>
+          <t>61,61%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>9596</t>
+          <t>10519</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>29635</t>
+          <t>30204</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>23,29%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>65,6%</t>
+          <t>66,86%</t>
         </is>
       </c>
     </row>
@@ -5053,7 +5053,7 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>8165</t>
+          <t>8568</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5068,7 +5068,7 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>30,1%</t>
+          <t>31,59%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>561</t>
+          <t>551</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>8752</t>
+          <t>8217</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>48,49%</t>
+          <t>45,53%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>1607</t>
+          <t>1825</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>11645</t>
+          <t>12199</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>25,78%</t>
+          <t>27,0%</t>
         </is>
       </c>
     </row>
@@ -5166,7 +5166,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>7626</t>
+          <t>6544</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5181,7 +5181,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>28,11%</t>
+          <t>24,12%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5196,12 +5196,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>839</t>
+          <t>863</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>9133</t>
+          <t>8585</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>50,6%</t>
+          <t>47,57%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>1496</t>
+          <t>1317</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>10161</t>
+          <t>10273</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>22,49%</t>
+          <t>22,74%</t>
         </is>
       </c>
     </row>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>1473</t>
+          <t>1513</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>14181</t>
+          <t>13247</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5289,12 +5289,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>52,28%</t>
+          <t>48,83%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5309,12 +5309,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>582</t>
+          <t>569</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>9852</t>
+          <t>10187</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5324,12 +5324,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>54,59%</t>
+          <t>56,44%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5344,12 +5344,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>3571</t>
+          <t>3781</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>18801</t>
+          <t>19200</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5359,12 +5359,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>41,62%</t>
+          <t>42,5%</t>
         </is>
       </c>
     </row>
@@ -5504,12 +5504,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>1881</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5519,12 +5519,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5539,12 +5539,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>1448</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>1706</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -5617,12 +5617,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>1090</t>
+          <t>1008</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>8753</t>
+          <t>8620</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5632,12 +5632,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>46,48%</t>
+          <t>45,77%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5657,7 +5657,7 @@
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>6689</t>
+          <t>8546</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5672,7 +5672,7 @@
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>41,8%</t>
+          <t>53,41%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5687,12 +5687,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>2731</t>
+          <t>2834</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>12585</t>
+          <t>12696</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5702,12 +5702,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>36,13%</t>
+          <t>36,45%</t>
         </is>
       </c>
     </row>
@@ -5730,12 +5730,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>1793</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>10577</t>
+          <t>10400</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5745,12 +5745,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>56,17%</t>
+          <t>55,22%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5765,12 +5765,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>3193</t>
+          <t>3691</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>10595</t>
+          <t>10928</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5780,12 +5780,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>23,07%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>66,21%</t>
+          <t>68,29%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5800,12 +5800,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>7075</t>
+          <t>7367</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>18242</t>
+          <t>17990</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5815,12 +5815,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>21,15%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>52,37%</t>
+          <t>51,65%</t>
         </is>
       </c>
     </row>
@@ -5848,7 +5848,7 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>7965</t>
+          <t>7975</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5863,7 +5863,7 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>42,3%</t>
+          <t>42,35%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5878,12 +5878,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>696</t>
+          <t>748</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>6185</t>
+          <t>6160</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5893,12 +5893,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>38,65%</t>
+          <t>38,5%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5913,12 +5913,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>2243</t>
+          <t>2226</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>11721</t>
+          <t>11106</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5928,12 +5928,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>33,65%</t>
+          <t>31,88%</t>
         </is>
       </c>
     </row>
@@ -5956,12 +5956,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>3014</t>
+          <t>3027</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>10921</t>
+          <t>10871</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>57,99%</t>
+          <t>57,72%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5991,12 +5991,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>1433</t>
+          <t>1348</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>7564</t>
+          <t>7935</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6006,12 +6006,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>47,27%</t>
+          <t>49,59%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6026,12 +6026,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>6017</t>
+          <t>5570</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>16225</t>
+          <t>15624</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6041,12 +6041,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>46,58%</t>
+          <t>44,85%</t>
         </is>
       </c>
     </row>
@@ -6186,12 +6186,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>959</t>
+          <t>1061</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>10631</t>
+          <t>10875</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6221,12 +6221,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>1105</t>
+          <t>1374</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>13385</t>
+          <t>13723</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6236,12 +6236,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>24,51%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6256,12 +6256,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>3124</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>18604</t>
+          <t>17308</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -6271,12 +6271,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>11,12%</t>
         </is>
       </c>
     </row>
@@ -6299,12 +6299,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>36048</t>
+          <t>34847</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>66550</t>
+          <t>63793</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6314,12 +6314,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>36,15%</t>
+          <t>34,95%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>66,74%</t>
+          <t>63,97%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6334,12 +6334,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>7419</t>
+          <t>7628</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>22233</t>
+          <t>22522</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6349,12 +6349,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>39,71%</t>
+          <t>40,23%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6369,12 +6369,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>46507</t>
+          <t>48463</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>84055</t>
+          <t>84908</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -6384,12 +6384,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>29,87%</t>
+          <t>31,12%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>53,98%</t>
+          <t>54,53%</t>
         </is>
       </c>
     </row>
@@ -6412,12 +6412,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>7731</t>
+          <t>6888</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>25226</t>
+          <t>25223</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6427,12 +6427,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>25,3%</t>
+          <t>25,29%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6447,12 +6447,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>7108</t>
+          <t>6887</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>19171</t>
+          <t>19611</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6462,12 +6462,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>34,24%</t>
+          <t>35,03%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6482,12 +6482,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>16595</t>
+          <t>16171</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>39400</t>
+          <t>37925</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -6497,12 +6497,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>25,3%</t>
+          <t>24,36%</t>
         </is>
       </c>
     </row>
@@ -6525,12 +6525,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>3631</t>
+          <t>3712</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>25465</t>
+          <t>23690</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -6540,12 +6540,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>25,54%</t>
+          <t>23,76%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -6560,12 +6560,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>3261</t>
+          <t>3133</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>12828</t>
+          <t>13018</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6575,12 +6575,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>22,91%</t>
+          <t>23,25%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6595,12 +6595,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>9287</t>
+          <t>9314</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>30571</t>
+          <t>30126</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -6610,12 +6610,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>19,35%</t>
         </is>
       </c>
     </row>
@@ -6638,12 +6638,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>11946</t>
+          <t>11823</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>32469</t>
+          <t>33297</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -6653,12 +6653,12 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>32,56%</t>
+          <t>33,39%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>12004</t>
+          <t>12017</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>26716</t>
+          <t>27411</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -6688,12 +6688,12 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>21,46%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>47,72%</t>
+          <t>48,96%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6708,12 +6708,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>26126</t>
+          <t>26933</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>52429</t>
+          <t>53235</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -6723,12 +6723,12 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>17,3%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>33,67%</t>
+          <t>34,19%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P25F_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P25F_2023-Provincia-trans_orig.xlsx
@@ -725,7 +725,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>1386</t>
+          <t>1202</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -735,12 +735,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8597</t>
+          <t>6046</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>67,83%</t>
+          <t>54,01%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>1386</t>
+          <t>1202</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
@@ -805,12 +805,12 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6711</t>
+          <t>5742</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>49,26%</t>
+          <t>47,2%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>8175</t>
+          <t>6387</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>347</t>
+          <t>2108</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12431</t>
+          <t>10272</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>64,5%</t>
+          <t>57,06%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>18,83%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>91,76%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>8175</t>
+          <t>6387</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>1975</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>13089</t>
+          <t>10547</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>60,01%</t>
+          <t>52,5%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>16,23%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>86,7%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3113</t>
+          <t>3605</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9983</t>
+          <t>8025</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>24,56%</t>
+          <t>32,2%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>78,77%</t>
+          <t>71,69%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>3113</t>
+          <t>3605</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>829</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>9090</t>
+          <t>8000</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>29,63%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>66,73%</t>
+          <t>65,77%</t>
         </is>
       </c>
     </row>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>949</t>
+          <t>971</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>949</t>
+          <t>971</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3780</t>
+          <t>3845</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>27,75%</t>
+          <t>31,6%</t>
         </is>
       </c>
     </row>
@@ -1290,17 +1290,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12674</t>
+          <t>11194</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>12674</t>
+          <t>11194</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12674</t>
+          <t>11194</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1325,17 +1325,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>949</t>
+          <t>971</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>949</t>
+          <t>971</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>949</t>
+          <t>971</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>13623</t>
+          <t>12165</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>13623</t>
+          <t>12165</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>13623</t>
+          <t>12165</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>598</t>
+          <t>610</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2951</t>
+          <t>3416</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>59,46%</t>
+          <t>61,38%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,7 +1477,7 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>598</t>
+          <t>610</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3883</t>
+          <t>4391</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>13,11%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>19406</t>
+          <t>17148</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7902</t>
+          <t>7444</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>25712</t>
+          <t>23873</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>68,86%</t>
+          <t>61,38%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>28,04%</t>
+          <t>26,64%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>91,23%</t>
+          <t>85,45%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>19405</t>
+          <t>17148</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>8116</t>
+          <t>8739</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>27937</t>
+          <t>25025</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>58,55%</t>
+          <t>51,18%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>24,49%</t>
+          <t>26,08%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>84,29%</t>
+          <t>74,69%</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3339</t>
+          <t>4810</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1643,12 +1643,12 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>13964</t>
+          <t>14519</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>49,55%</t>
+          <t>51,97%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1703,7 +1703,7 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>3339</t>
+          <t>4810</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
@@ -1713,12 +1713,12 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>16444</t>
+          <t>15462</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>49,61%</t>
+          <t>46,15%</t>
         </is>
       </c>
     </row>
@@ -1746,7 +1746,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3961</t>
+          <t>3308</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1756,12 +1756,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16097</t>
+          <t>12621</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1771,7 +1771,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>57,12%</t>
+          <t>45,18%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>3961</t>
+          <t>3308</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
@@ -1826,12 +1826,12 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>16115</t>
+          <t>15132</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
@@ -1841,7 +1841,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>48,62%</t>
+          <t>45,17%</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1477</t>
+          <t>2672</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1869,12 +1869,12 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>8338</t>
+          <t>8536</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1884,7 +1884,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>29,59%</t>
+          <t>30,55%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1894,27 +1894,27 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>4365</t>
+          <t>4955</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2130</t>
+          <t>2136</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4963</t>
+          <t>5565</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>87,95%</t>
+          <t>89,05%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>42,91%</t>
+          <t>38,38%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>5841</t>
+          <t>7628</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1762</t>
+          <t>2728</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>14008</t>
+          <t>14697</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>22,77%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>42,26%</t>
+          <t>43,87%</t>
         </is>
       </c>
     </row>
@@ -1972,17 +1972,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>28182</t>
+          <t>27938</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>28182</t>
+          <t>27938</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>28182</t>
+          <t>27938</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2007,17 +2007,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>4963</t>
+          <t>5565</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>4963</t>
+          <t>5565</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>4963</t>
+          <t>5565</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>33144</t>
+          <t>33503</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>33144</t>
+          <t>33503</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>33144</t>
+          <t>33503</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2350,7 +2350,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>648</t>
+          <t>673</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
@@ -2360,12 +2360,12 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1896</t>
+          <t>2486</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>26,64%</t>
+          <t>27,08%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
@@ -2375,7 +2375,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>77,92%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,7 +2385,7 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>648</t>
+          <t>673</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
@@ -2395,12 +2395,12 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>3441</t>
+          <t>4043</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>43,48%</t>
+          <t>52,36%</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2287</t>
+          <t>2200</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -2438,12 +2438,12 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5481</t>
+          <t>5235</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>41,73%</t>
+          <t>42,03%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>2288</t>
+          <t>2200</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
@@ -2508,12 +2508,12 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5912</t>
+          <t>5348</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>28,9%</t>
+          <t>28,49%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>74,69%</t>
+          <t>69,27%</t>
         </is>
       </c>
     </row>
@@ -2541,7 +2541,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>3194</t>
+          <t>3035</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -2551,12 +2551,12 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5481</t>
+          <t>5235</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>58,27%</t>
+          <t>57,97%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -2576,27 +2576,27 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>1785</t>
+          <t>1813</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>351</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>2433</t>
+          <t>2486</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>73,36%</t>
+          <t>72,92%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>4848</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1970</t>
+          <t>1824</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>7331</t>
+          <t>7048</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>62,91%</t>
+          <t>62,79%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>24,89%</t>
+          <t>23,63%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>92,62%</t>
+          <t>91,28%</t>
         </is>
       </c>
     </row>
@@ -2654,17 +2654,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>5481</t>
+          <t>5235</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>5481</t>
+          <t>5235</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5481</t>
+          <t>5235</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2689,17 +2689,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>2433</t>
+          <t>2486</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2433</t>
+          <t>2486</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>2433</t>
+          <t>2486</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>7915</t>
+          <t>7721</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>7915</t>
+          <t>7721</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>7915</t>
+          <t>7721</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>2711</t>
+          <t>6234</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>5210</t>
+          <t>9009</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>52,03%</t>
+          <t>69,2%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -2919,32 +2919,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>4005</t>
+          <t>5779</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>671</t>
+          <t>1646</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>7163</t>
+          <t>9022</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>51,16%</t>
+          <t>56,33%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>16,04%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>91,51%</t>
+          <t>87,94%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2954,32 +2954,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>6715</t>
+          <t>12013</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1868</t>
+          <t>5115</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>11248</t>
+          <t>17353</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>51,5%</t>
+          <t>62,35%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>26,55%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>86,28%</t>
+          <t>90,06%</t>
         </is>
       </c>
     </row>
@@ -3032,7 +3032,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1551</t>
+          <t>1691</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
@@ -3042,12 +3042,12 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>5684</t>
+          <t>6724</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
@@ -3057,7 +3057,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>72,61%</t>
+          <t>65,55%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3067,7 +3067,7 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1551</t>
+          <t>1691</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
@@ -3077,12 +3077,12 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6952</t>
+          <t>7988</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
@@ -3092,7 +3092,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>53,33%</t>
+          <t>41,46%</t>
         </is>
       </c>
     </row>
@@ -3145,7 +3145,7 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>666</t>
+          <t>658</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
@@ -3155,12 +3155,12 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>4175</t>
+          <t>4046</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
@@ -3170,7 +3170,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>53,33%</t>
+          <t>39,44%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,7 +3180,7 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>666</t>
+          <t>658</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
@@ -3190,12 +3190,12 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4391</t>
+          <t>3898</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
@@ -3205,7 +3205,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>33,68%</t>
+          <t>20,23%</t>
         </is>
       </c>
     </row>
@@ -3223,7 +3223,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>2499</t>
+          <t>2775</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -3233,12 +3233,12 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>5043</t>
+          <t>9009</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>47,97%</t>
+          <t>30,8%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -3248,7 +3248,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>1606</t>
+          <t>2131</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
@@ -3268,12 +3268,12 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>6221</t>
+          <t>6360</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>20,77%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>79,47%</t>
+          <t>61,99%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>4105</t>
+          <t>4905</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>686</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>9331</t>
+          <t>12732</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>31,49%</t>
+          <t>25,46%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>71,57%</t>
+          <t>66,08%</t>
         </is>
       </c>
     </row>
@@ -3336,17 +3336,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>5210</t>
+          <t>9009</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>5210</t>
+          <t>9009</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>5210</t>
+          <t>9009</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3371,17 +3371,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>7828</t>
+          <t>10259</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>7828</t>
+          <t>10259</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>7828</t>
+          <t>10259</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>13037</t>
+          <t>19268</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>13037</t>
+          <t>19268</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>13037</t>
+          <t>19268</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3488,7 +3488,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>436</t>
+          <t>456</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
@@ -3498,12 +3498,12 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1863</t>
+          <t>1936</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
@@ -3513,7 +3513,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>60,25%</t>
+          <t>59,32%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3523,7 +3523,7 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>436</t>
+          <t>456</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
@@ -3533,12 +3533,12 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1944</t>
+          <t>2579</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
@@ -3548,7 +3548,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>43,56%</t>
+          <t>53,9%</t>
         </is>
       </c>
     </row>
@@ -3566,7 +3566,7 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>676</t>
+          <t>742</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -3576,12 +3576,12 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1370</t>
+          <t>1522</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>49,36%</t>
+          <t>48,76%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -3601,32 +3601,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>1442</t>
+          <t>1515</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>398</t>
+          <t>416</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2697</t>
+          <t>2849</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>46,61%</t>
+          <t>46,43%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>87,18%</t>
+          <t>87,32%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3636,32 +3636,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>2118</t>
+          <t>2257</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>769</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>3614</t>
+          <t>3895</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>47,46%</t>
+          <t>47,17%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>80,97%</t>
+          <t>81,41%</t>
         </is>
       </c>
     </row>
@@ -3714,7 +3714,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>425</t>
+          <t>471</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1836</t>
+          <t>1827</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
@@ -3739,7 +3739,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>59,35%</t>
+          <t>55,99%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3749,7 +3749,7 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>425</t>
+          <t>471</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>2277</t>
+          <t>2339</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
@@ -3774,7 +3774,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>51,02%</t>
+          <t>48,87%</t>
         </is>
       </c>
     </row>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>694</t>
+          <t>780</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>1370</t>
+          <t>1522</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>50,64%</t>
+          <t>51,24%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -3940,7 +3940,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>790</t>
+          <t>821</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
@@ -3950,12 +3950,12 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>2003</t>
+          <t>2147</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>25,16%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>64,77%</t>
+          <t>65,79%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3975,32 +3975,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>1483</t>
+          <t>1601</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>398</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>3181</t>
+          <t>3451</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>33,23%</t>
+          <t>33,46%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>71,28%</t>
+          <t>72,13%</t>
         </is>
       </c>
     </row>
@@ -4018,17 +4018,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>1370</t>
+          <t>1522</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>1370</t>
+          <t>1522</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>1370</t>
+          <t>1522</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4053,17 +4053,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>3093</t>
+          <t>3263</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>3093</t>
+          <t>3263</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>3093</t>
+          <t>3263</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,17 +4088,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>4463</t>
+          <t>4785</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>4463</t>
+          <t>4785</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>4463</t>
+          <t>4785</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4283,7 +4283,7 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>1182</t>
+          <t>1196</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
@@ -4293,12 +4293,12 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>2673</t>
+          <t>2638</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>44,24%</t>
+          <t>45,34%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
@@ -4318,7 +4318,7 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>1182</t>
+          <t>1196</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
@@ -4328,12 +4328,12 @@
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>3075</t>
+          <t>3308</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>33,61%</t>
+          <t>34,51%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
@@ -4343,7 +4343,7 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>87,4%</t>
+          <t>95,46%</t>
         </is>
       </c>
     </row>
@@ -4587,7 +4587,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>845</t>
+          <t>828</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -4622,7 +4622,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>1491</t>
+          <t>1442</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
@@ -4632,12 +4632,12 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>2673</t>
+          <t>2638</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>55,76%</t>
+          <t>54,66%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
@@ -4657,27 +4657,27 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>2336</t>
+          <t>2269</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>520</t>
+          <t>98</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>3518</t>
+          <t>3465</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>66,39%</t>
+          <t>65,49%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
@@ -4700,17 +4700,17 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>845</t>
+          <t>828</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>845</t>
+          <t>828</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>845</t>
+          <t>828</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4735,17 +4735,17 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>2673</t>
+          <t>2638</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>2673</t>
+          <t>2638</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>2673</t>
+          <t>2638</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4770,17 +4770,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>3518</t>
+          <t>3465</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>3518</t>
+          <t>3465</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>3518</t>
+          <t>3465</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4817,7 +4817,7 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>2503</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>8549</t>
+          <t>8604</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -4842,7 +4842,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>31,52%</t>
+          <t>27,47%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4852,7 +4852,7 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>3597</t>
+          <t>3415</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
@@ -4862,12 +4862,12 @@
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>11231</t>
+          <t>10663</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
@@ -4877,7 +4877,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>62,23%</t>
+          <t>46,67%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4887,32 +4887,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>6009</t>
+          <t>5918</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>1338</t>
+          <t>1392</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>14664</t>
+          <t>14338</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>32,46%</t>
+          <t>26,47%</t>
         </is>
       </c>
     </row>
@@ -4930,32 +4930,32 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>15266</t>
+          <t>17366</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>7265</t>
+          <t>9346</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>22237</t>
+          <t>24474</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>56,28%</t>
+          <t>55,44%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>26,78%</t>
+          <t>29,84%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>81,98%</t>
+          <t>78,13%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4965,32 +4965,32 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>4851</t>
+          <t>5765</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>383</t>
+          <t>1495</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>11119</t>
+          <t>12601</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>26,88%</t>
+          <t>25,23%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>61,61%</t>
+          <t>55,16%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5000,32 +5000,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>20116</t>
+          <t>23131</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>10519</t>
+          <t>13133</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>30204</t>
+          <t>34261</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>44,53%</t>
+          <t>42,7%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>24,24%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>66,86%</t>
+          <t>63,25%</t>
         </is>
       </c>
     </row>
@@ -5043,32 +5043,32 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>2474</t>
+          <t>3440</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>804</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>8568</t>
+          <t>9475</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>31,59%</t>
+          <t>30,25%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5078,32 +5078,32 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>2738</t>
+          <t>2873</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>551</t>
+          <t>617</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>8217</t>
+          <t>9260</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>45,53%</t>
+          <t>40,53%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5113,32 +5113,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>5212</t>
+          <t>6313</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>1825</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>12199</t>
+          <t>13521</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>27,0%</t>
+          <t>24,96%</t>
         </is>
       </c>
     </row>
@@ -5156,7 +5156,7 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>1296</t>
+          <t>2297</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>6544</t>
+          <t>7811</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -5181,7 +5181,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>24,12%</t>
+          <t>24,93%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5191,32 +5191,32 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>3295</t>
+          <t>7072</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>863</t>
+          <t>2462</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>8585</t>
+          <t>14095</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>30,96%</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>47,57%</t>
+          <t>61,7%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5226,32 +5226,32 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>4591</t>
+          <t>9369</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>1317</t>
+          <t>3978</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>10273</t>
+          <t>18271</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>17,3%</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>33,73%</t>
         </is>
       </c>
     </row>
@@ -5269,32 +5269,32 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>5678</t>
+          <t>5720</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>1513</t>
+          <t>1786</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>13247</t>
+          <t>13621</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>18,26%</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>48,83%</t>
+          <t>43,48%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5304,32 +5304,32 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>3568</t>
+          <t>3720</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>569</t>
+          <t>657</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>10187</t>
+          <t>10418</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>56,44%</t>
+          <t>45,6%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5339,32 +5339,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>9246</t>
+          <t>9439</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>3781</t>
+          <t>3776</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>19200</t>
+          <t>18794</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>42,5%</t>
+          <t>34,7%</t>
         </is>
       </c>
     </row>
@@ -5382,17 +5382,17 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>27126</t>
+          <t>31325</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>27126</t>
+          <t>31325</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>27126</t>
+          <t>31325</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5417,17 +5417,17 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>18048</t>
+          <t>22846</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>18048</t>
+          <t>22846</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>18048</t>
+          <t>22846</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5452,17 +5452,17 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>45174</t>
+          <t>54170</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>45174</t>
+          <t>54170</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>45174</t>
+          <t>54170</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5612,32 +5612,32 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>4229</t>
+          <t>4816</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>1008</t>
+          <t>1211</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>8620</t>
+          <t>10469</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>22,39%</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>45,77%</t>
+          <t>48,67%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5647,7 +5647,7 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>2338</t>
+          <t>2813</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
@@ -5657,12 +5657,12 @@
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>8546</t>
+          <t>9063</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
@@ -5672,7 +5672,7 @@
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>53,41%</t>
+          <t>50,43%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5682,32 +5682,32 @@
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>6567</t>
+          <t>7630</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>2834</t>
+          <t>3177</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>12696</t>
+          <t>14156</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>19,33%</t>
         </is>
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>36,45%</t>
+          <t>35,86%</t>
         </is>
       </c>
     </row>
@@ -5725,32 +5725,32 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>5435</t>
+          <t>6133</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>1793</t>
+          <t>2129</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>10400</t>
+          <t>11446</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>28,86%</t>
+          <t>28,51%</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>55,22%</t>
+          <t>53,21%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5760,32 +5760,32 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>6769</t>
+          <t>7545</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>3691</t>
+          <t>3665</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>10928</t>
+          <t>11922</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>42,3%</t>
+          <t>41,99%</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>20,4%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>68,29%</t>
+          <t>66,35%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5795,32 +5795,32 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>12204</t>
+          <t>13678</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>7367</t>
+          <t>7868</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>17990</t>
+          <t>19926</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
         <is>
-          <t>35,03%</t>
+          <t>34,65%</t>
         </is>
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>19,93%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>51,65%</t>
+          <t>50,47%</t>
         </is>
       </c>
     </row>
@@ -5838,7 +5838,7 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>2760</t>
+          <t>3067</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -5848,12 +5848,12 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>7975</t>
+          <t>8486</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -5863,7 +5863,7 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>42,35%</t>
+          <t>39,45%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5873,7 +5873,7 @@
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>2905</t>
+          <t>3160</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
@@ -5883,22 +5883,22 @@
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>6160</t>
+          <t>6622</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>38,5%</t>
+          <t>36,85%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5908,32 +5908,32 @@
       </c>
       <c r="R49" s="2" t="inlineStr">
         <is>
-          <t>5665</t>
+          <t>6227</t>
         </is>
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>2226</t>
+          <t>2619</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>11106</t>
+          <t>13080</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>31,88%</t>
+          <t>33,13%</t>
         </is>
       </c>
     </row>
@@ -5951,32 +5951,32 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>6408</t>
+          <t>7493</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>3027</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>10871</t>
+          <t>12640</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>34,03%</t>
+          <t>34,84%</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>57,72%</t>
+          <t>58,77%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5986,32 +5986,32 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>3990</t>
+          <t>4450</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>1348</t>
+          <t>1510</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>7935</t>
+          <t>8812</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>24,94%</t>
+          <t>24,77%</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>49,59%</t>
+          <t>49,04%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6021,32 +6021,32 @@
       </c>
       <c r="R50" s="2" t="inlineStr">
         <is>
-          <t>10398</t>
+          <t>11943</t>
         </is>
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>5570</t>
+          <t>7083</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>15624</t>
+          <t>18341</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
         <is>
-          <t>29,85%</t>
+          <t>30,25%</t>
         </is>
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>44,85%</t>
+          <t>46,46%</t>
         </is>
       </c>
     </row>
@@ -6064,17 +6064,17 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>18832</t>
+          <t>21509</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>18832</t>
+          <t>21509</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>18832</t>
+          <t>21509</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -6099,17 +6099,17 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>16002</t>
+          <t>17969</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>16002</t>
+          <t>17969</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>16002</t>
+          <t>17969</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6134,17 +6134,17 @@
       </c>
       <c r="R51" s="2" t="inlineStr">
         <is>
-          <t>34834</t>
+          <t>39478</t>
         </is>
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>34834</t>
+          <t>39478</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>34834</t>
+          <t>39478</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
@@ -6181,32 +6181,32 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>3798</t>
+          <t>3704</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>1061</t>
+          <t>1120</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>10875</t>
+          <t>10948</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6216,32 +6216,32 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>4631</t>
+          <t>4480</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>1374</t>
+          <t>1139</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>13723</t>
+          <t>12983</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>24,51%</t>
+          <t>19,67%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6251,32 +6251,32 @@
       </c>
       <c r="R52" s="2" t="inlineStr">
         <is>
-          <t>8429</t>
+          <t>8185</t>
         </is>
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>3124</t>
+          <t>3002</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>17308</t>
+          <t>17127</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>9,81%</t>
         </is>
       </c>
     </row>
@@ -6294,32 +6294,32 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>50461</t>
+          <t>52694</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>34847</t>
+          <t>36655</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>63793</t>
+          <t>67000</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>50,6%</t>
+          <t>48,54%</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>34,95%</t>
+          <t>33,77%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>63,97%</t>
+          <t>61,72%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6329,32 +6329,32 @@
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>13818</t>
+          <t>17068</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>7628</t>
+          <t>9132</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>22522</t>
+          <t>25710</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>24,68%</t>
+          <t>25,86%</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>40,23%</t>
+          <t>38,96%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6364,32 +6364,32 @@
       </c>
       <c r="R53" s="2" t="inlineStr">
         <is>
-          <t>64279</t>
+          <t>69762</t>
         </is>
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>48463</t>
+          <t>52095</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>84908</t>
+          <t>88732</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
         <is>
-          <t>41,28%</t>
+          <t>39,97%</t>
         </is>
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>31,12%</t>
+          <t>29,84%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>54,53%</t>
+          <t>50,83%</t>
         </is>
       </c>
     </row>
@@ -6407,32 +6407,32 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>14362</t>
+          <t>17988</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>6888</t>
+          <t>9700</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>25223</t>
+          <t>29336</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>16,57%</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>27,02%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6442,32 +6442,32 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>12130</t>
+          <t>13254</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>6887</t>
+          <t>7673</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>19611</t>
+          <t>21268</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>20,08%</t>
         </is>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>35,03%</t>
+          <t>32,23%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6477,32 +6477,32 @@
       </c>
       <c r="R54" s="2" t="inlineStr">
         <is>
-          <t>26492</t>
+          <t>31242</t>
         </is>
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>16171</t>
+          <t>20258</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>37925</t>
+          <t>45504</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>17,9%</t>
         </is>
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>26,07%</t>
         </is>
       </c>
     </row>
@@ -6520,32 +6520,32 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>10304</t>
+          <t>10872</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>3712</t>
+          <t>4837</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>23690</t>
+          <t>23850</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>23,76%</t>
+          <t>21,97%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -6555,32 +6555,32 @@
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>6866</t>
+          <t>10890</t>
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>3133</t>
+          <t>5490</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>13018</t>
+          <t>18830</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>16,5%</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>28,53%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6590,32 +6590,32 @@
       </c>
       <c r="R55" s="2" t="inlineStr">
         <is>
-          <t>17170</t>
+          <t>21762</t>
         </is>
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>9314</t>
+          <t>12426</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>30126</t>
+          <t>34659</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>19,86%</t>
         </is>
       </c>
     </row>
@@ -6633,32 +6633,32 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>20793</t>
+          <t>23302</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>11823</t>
+          <t>14660</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>33297</t>
+          <t>35994</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>21,46%</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>33,39%</t>
+          <t>33,16%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6668,32 +6668,32 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>18544</t>
+          <t>20303</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>12017</t>
+          <t>13900</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>27411</t>
+          <t>29584</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>30,76%</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>21,06%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>48,96%</t>
+          <t>44,83%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6703,32 +6703,32 @@
       </c>
       <c r="R56" s="2" t="inlineStr">
         <is>
-          <t>39337</t>
+          <t>43605</t>
         </is>
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>26933</t>
+          <t>30701</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>53235</t>
+          <t>58207</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
         <is>
-          <t>25,26%</t>
+          <t>24,98%</t>
         </is>
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>34,19%</t>
+          <t>33,35%</t>
         </is>
       </c>
     </row>
@@ -6746,17 +6746,17 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>99719</t>
+          <t>108560</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>99719</t>
+          <t>108560</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>99719</t>
+          <t>108560</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -6781,17 +6781,17 @@
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>55989</t>
+          <t>65995</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>55989</t>
+          <t>65995</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>55989</t>
+          <t>65995</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -6816,17 +6816,17 @@
       </c>
       <c r="R57" s="2" t="inlineStr">
         <is>
-          <t>155708</t>
+          <t>174555</t>
         </is>
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>155708</t>
+          <t>174555</t>
         </is>
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>155708</t>
+          <t>174555</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
